--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.490334987640381</v>
+        <v>1.4497971534729</v>
       </c>
       <c r="E2" t="n">
         <v>0.9993661750125149</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.339414834976196</v>
+        <v>2.304472208023071</v>
       </c>
       <c r="E3" t="n">
         <v>0.9994024065876171</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.490334987640381</v>
+        <v>1.4497971534729</v>
       </c>
       <c r="E2" t="n">
         <v>0.9993661750125149</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.339414834976196</v>
+        <v>2.304472208023071</v>
       </c>
       <c r="E3" t="n">
         <v>0.9994024065876171</v>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4497971534729</v>
+        <v>1.937947750091553</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9993661750125149</v>
+        <v>0.9916672509648135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9997201460968009</v>
+        <v>0.9926310374474091</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3296664859921038</v>
+        <v>1.691656918987547</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2273045995670993</v>
+        <v>1.079954545454545</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.304472208023071</v>
+        <v>2.616126298904419</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9994024065876171</v>
+        <v>0.991944820007945</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997201460968009</v>
+        <v>0.9924359336701404</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3296664859921038</v>
+        <v>1.713905130730069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2273045995670993</v>
+        <v>1.105564935064935</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4497971534729</v>
+        <v>1.937947750091553</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9993661750125149</v>
+        <v>0.9916672509648135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9997201460968009</v>
+        <v>0.9926310374474091</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3296664859921038</v>
+        <v>1.691656918987547</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2273045995670993</v>
+        <v>1.079954545454545</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.304472208023071</v>
+        <v>2.616126298904419</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9994024065876171</v>
+        <v>0.991944820007945</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997201460968009</v>
+        <v>0.9924359336701404</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3296664859921038</v>
+        <v>1.713905130730069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2273045995670993</v>
+        <v>1.105564935064935</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.937947750091553</v>
+        <v>20.71422243118286</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9916672509648135</v>
+        <v>0.944157492185361</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9926310374474091</v>
+        <v>0.949013231773535</v>
       </c>
       <c r="G2" t="n">
-        <v>1.691656918987547</v>
+        <v>40.1810526070136</v>
       </c>
       <c r="H2" t="n">
-        <v>1.079954545454545</v>
+        <v>23.79068469505178</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,21 +526,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.616126298904419</v>
+        <v>39.83931756019592</v>
       </c>
       <c r="E3" t="n">
-        <v>0.991944820007945</v>
+        <v>0.9469375966432583</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9924359336701404</v>
+        <v>0.949013231773535</v>
       </c>
       <c r="G3" t="n">
-        <v>1.713905130730069</v>
+        <v>40.1810526070136</v>
       </c>
       <c r="H3" t="n">
-        <v>1.105564935064935</v>
+        <v>23.79068469505178</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>86.38496446609497</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9491455793684336</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9499988975446574</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.7907712481769</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.77624280782508</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,19 +657,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.937947750091553</v>
+        <v>20.71422243118286</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9916672509648135</v>
+        <v>0.944157492185361</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9926310374474091</v>
+        <v>0.949013231773535</v>
       </c>
       <c r="G2" t="n">
-        <v>1.691656918987547</v>
+        <v>40.1810526070136</v>
       </c>
       <c r="H2" t="n">
-        <v>1.079954545454545</v>
+        <v>23.79068469505178</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,21 +692,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.616126298904419</v>
+        <v>39.83931756019592</v>
       </c>
       <c r="E3" t="n">
-        <v>0.991944820007945</v>
+        <v>0.9469375966432583</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9924359336701404</v>
+        <v>0.949013231773535</v>
       </c>
       <c r="G3" t="n">
-        <v>1.713905130730069</v>
+        <v>40.1810526070136</v>
       </c>
       <c r="H3" t="n">
-        <v>1.105564935064935</v>
+        <v>23.79068469505178</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>86.38496446609497</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9491455793684336</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9499988975446574</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.7907712481769</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.77624280782508</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,13 +488,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>20.71422243118286</v>
+        <v>773.1986422538757</v>
       </c>
       <c r="E2" t="n">
-        <v>0.944157492185361</v>
+        <v>0.9503921749831643</v>
       </c>
       <c r="F2" t="n">
         <v>0.949013231773535</v>
@@ -523,13 +523,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>39.83931756019592</v>
+        <v>115.5476741790771</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9469375966432583</v>
+        <v>0.9497617034790053</v>
       </c>
       <c r="F3" t="n">
         <v>0.949013231773535</v>
@@ -543,41 +543,6 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>86.38496446609497</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9491455793684336</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9499988975446574</v>
-      </c>
-      <c r="G4" t="n">
-        <v>39.7907712481769</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.77624280782508</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,13 +619,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>20.71422243118286</v>
+        <v>773.1986422538757</v>
       </c>
       <c r="E2" t="n">
-        <v>0.944157492185361</v>
+        <v>0.9503921749831643</v>
       </c>
       <c r="F2" t="n">
         <v>0.949013231773535</v>
@@ -689,13 +654,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>39.83931756019592</v>
+        <v>115.5476741790771</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9469375966432583</v>
+        <v>0.9497617034790053</v>
       </c>
       <c r="F3" t="n">
         <v>0.949013231773535</v>
@@ -709,41 +674,6 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>86.38496446609497</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9491455793684336</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9499988975446574</v>
-      </c>
-      <c r="G4" t="n">
-        <v>39.7907712481769</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.77624280782508</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -488,22 +488,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>773.1986422538757</v>
+        <v>1.29323148727417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9503921749831643</v>
+        <v>0.9916672509648135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.949013231773535</v>
+        <v>0.9926310374474091</v>
       </c>
       <c r="G2" t="n">
-        <v>40.1810526070136</v>
+        <v>1.691656918987547</v>
       </c>
       <c r="H2" t="n">
-        <v>23.79068469505178</v>
+        <v>1.079954545454545</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>115.5476741790771</v>
+        <v>1.950638294219971</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9497617034790053</v>
+        <v>0.991944820007945</v>
       </c>
       <c r="F3" t="n">
-        <v>0.949013231773535</v>
+        <v>0.9924359336701404</v>
       </c>
       <c r="G3" t="n">
-        <v>40.1810526070136</v>
+        <v>1.713905130730069</v>
       </c>
       <c r="H3" t="n">
-        <v>23.79068469505178</v>
+        <v>1.105564935064935</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -619,22 +619,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>773.1986422538757</v>
+        <v>1.29323148727417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9503921749831643</v>
+        <v>0.9916672509648135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.949013231773535</v>
+        <v>0.9926310374474091</v>
       </c>
       <c r="G2" t="n">
-        <v>40.1810526070136</v>
+        <v>1.691656918987547</v>
       </c>
       <c r="H2" t="n">
-        <v>23.79068469505178</v>
+        <v>1.079954545454545</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>115.5476741790771</v>
+        <v>1.950638294219971</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9497617034790053</v>
+        <v>0.991944820007945</v>
       </c>
       <c r="F3" t="n">
-        <v>0.949013231773535</v>
+        <v>0.9924359336701404</v>
       </c>
       <c r="G3" t="n">
-        <v>40.1810526070136</v>
+        <v>1.713905130730069</v>
       </c>
       <c r="H3" t="n">
-        <v>23.79068469505178</v>
+        <v>1.105564935064935</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.29323148727417</v>
+        <v>2.513111352920532</v>
       </c>
       <c r="E2" t="n">
         <v>0.9916672509648135</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.950638294219971</v>
+        <v>3.599078893661499</v>
       </c>
       <c r="E3" t="n">
         <v>0.991944820007945</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.29323148727417</v>
+        <v>2.513111352920532</v>
       </c>
       <c r="E2" t="n">
         <v>0.9916672509648135</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.950638294219971</v>
+        <v>3.599078893661499</v>
       </c>
       <c r="E3" t="n">
         <v>0.991944820007945</v>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.513111352920532</v>
+        <v>2.404082775115967</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9916672509648135</v>
+        <v>0.9914408909760367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9926310374474091</v>
+        <v>0.9918322661383299</v>
       </c>
       <c r="G2" t="n">
-        <v>1.691656918987547</v>
+        <v>1.780983531866373</v>
       </c>
       <c r="H2" t="n">
-        <v>1.079954545454545</v>
+        <v>1.170763636363636</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.599078893661499</v>
+        <v>3.604471683502197</v>
       </c>
       <c r="E3" t="n">
-        <v>0.991944820007945</v>
+        <v>0.9918212871921988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9924359336701404</v>
+        <v>0.9923259444363434</v>
       </c>
       <c r="G3" t="n">
-        <v>1.713905130730069</v>
+        <v>1.726321122047857</v>
       </c>
       <c r="H3" t="n">
-        <v>1.105564935064935</v>
+        <v>1.109712337662338</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.513111352920532</v>
+        <v>2.404082775115967</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9916672509648135</v>
+        <v>0.9914408909760367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9926310374474091</v>
+        <v>0.9918322661383299</v>
       </c>
       <c r="G2" t="n">
-        <v>1.691656918987547</v>
+        <v>1.780983531866373</v>
       </c>
       <c r="H2" t="n">
-        <v>1.079954545454545</v>
+        <v>1.170763636363636</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.599078893661499</v>
+        <v>3.604471683502197</v>
       </c>
       <c r="E3" t="n">
-        <v>0.991944820007945</v>
+        <v>0.9918212871921988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9924359336701404</v>
+        <v>0.9923259444363434</v>
       </c>
       <c r="G3" t="n">
-        <v>1.713905130730069</v>
+        <v>1.726321122047857</v>
       </c>
       <c r="H3" t="n">
-        <v>1.105564935064935</v>
+        <v>1.109712337662338</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.404082775115967</v>
+        <v>0.9581782817840576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9914408909760367</v>
+        <v>0.9914238516975447</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9918322661383299</v>
+        <v>0.9920354917748463</v>
       </c>
       <c r="G2" t="n">
-        <v>1.780983531866373</v>
+        <v>1.758687177428648</v>
       </c>
       <c r="H2" t="n">
-        <v>1.170763636363636</v>
+        <v>1.129233766233765</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 50}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.604471683502197</v>
+        <v>1.731677055358887</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918212871921988</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.404082775115967</v>
+        <v>0.9581782817840576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9914408909760367</v>
+        <v>0.9914238516975447</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9918322661383299</v>
+        <v>0.9920354917748463</v>
       </c>
       <c r="G2" t="n">
-        <v>1.780983531866373</v>
+        <v>1.758687177428648</v>
       </c>
       <c r="H2" t="n">
-        <v>1.170763636363636</v>
+        <v>1.129233766233765</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 50}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.604471683502197</v>
+        <v>1.731677055358887</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918212871921988</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9581782817840576</v>
+        <v>21.75919961929321</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9914238516975447</v>
+        <v>0.944227051557548</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9920354917748463</v>
+        <v>0.9498091161774663</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758687177428648</v>
+        <v>39.86621353453122</v>
       </c>
       <c r="H2" t="n">
-        <v>1.129233766233765</v>
+        <v>23.61910385500575</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.731677055358887</v>
+        <v>40.380699634552</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918212871921988</v>
+        <v>0.9471150885859518</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9923259444363434</v>
+        <v>0.9502406638435245</v>
       </c>
       <c r="G3" t="n">
-        <v>1.726321122047857</v>
+        <v>39.69445612706919</v>
       </c>
       <c r="H3" t="n">
-        <v>1.109712337662338</v>
+        <v>23.63055235903337</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9581782817840576</v>
+        <v>21.75919961929321</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9914238516975447</v>
+        <v>0.944227051557548</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9920354917748463</v>
+        <v>0.9498091161774663</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758687177428648</v>
+        <v>39.86621353453122</v>
       </c>
       <c r="H2" t="n">
-        <v>1.129233766233765</v>
+        <v>23.61910385500575</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.731677055358887</v>
+        <v>40.380699634552</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918212871921988</v>
+        <v>0.9471150885859518</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9923259444363434</v>
+        <v>0.9502406638435245</v>
       </c>
       <c r="G3" t="n">
-        <v>1.726321122047857</v>
+        <v>39.69445612706919</v>
       </c>
       <c r="H3" t="n">
-        <v>1.109712337662338</v>
+        <v>23.63055235903337</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>21.75919961929321</v>
+        <v>4.515264987945557</v>
       </c>
       <c r="E2" t="n">
-        <v>0.944227051557548</v>
+        <v>0.4705013619511558</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9498091161774663</v>
+        <v>0.5601484541981341</v>
       </c>
       <c r="G2" t="n">
-        <v>39.86621353453122</v>
+        <v>0.5836550403591331</v>
       </c>
       <c r="H2" t="n">
-        <v>23.61910385500575</v>
+        <v>0.4202984693877552</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>40.380699634552</v>
+        <v>8.012170791625977</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9471150885859518</v>
+        <v>0.4966990621142527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9502406638435245</v>
+        <v>0.5601484541981341</v>
       </c>
       <c r="G3" t="n">
-        <v>39.69445612706919</v>
+        <v>0.5836550403591331</v>
       </c>
       <c r="H3" t="n">
-        <v>23.63055235903337</v>
+        <v>0.4202984693877552</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>21.75919961929321</v>
+        <v>4.515264987945557</v>
       </c>
       <c r="E2" t="n">
-        <v>0.944227051557548</v>
+        <v>0.4705013619511558</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9498091161774663</v>
+        <v>0.5601484541981341</v>
       </c>
       <c r="G2" t="n">
-        <v>39.86621353453122</v>
+        <v>0.5836550403591331</v>
       </c>
       <c r="H2" t="n">
-        <v>23.61910385500575</v>
+        <v>0.4202984693877552</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>40.380699634552</v>
+        <v>8.012170791625977</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9471150885859518</v>
+        <v>0.4966990621142527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9502406638435245</v>
+        <v>0.5601484541981341</v>
       </c>
       <c r="G3" t="n">
-        <v>39.69445612706919</v>
+        <v>0.5836550403591331</v>
       </c>
       <c r="H3" t="n">
-        <v>23.63055235903337</v>
+        <v>0.4202984693877552</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.515264987945557</v>
+        <v>60.9213080406189</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4705013619511558</v>
+        <v>0.5059173107368674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5601484541981341</v>
+        <v>0.589358628410138</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5836550403591331</v>
+        <v>64.1040218121336</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4202984693877552</v>
+        <v>30.19281732961743</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.012170791625977</v>
+        <v>119.1835825443268</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4966990621142527</v>
+        <v>0.5359470634249959</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5601484541981341</v>
+        <v>0.589358628410138</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5836550403591331</v>
+        <v>64.1040218121336</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4202984693877552</v>
+        <v>30.19281732961743</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.515264987945557</v>
+        <v>60.9213080406189</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4705013619511558</v>
+        <v>0.5059173107368674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5601484541981341</v>
+        <v>0.589358628410138</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5836550403591331</v>
+        <v>64.1040218121336</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4202984693877552</v>
+        <v>30.19281732961743</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.012170791625977</v>
+        <v>119.1835825443268</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4966990621142527</v>
+        <v>0.5359470634249959</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5601484541981341</v>
+        <v>0.589358628410138</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5836550403591331</v>
+        <v>64.1040218121336</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4202984693877552</v>
+        <v>30.19281732961743</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>60.9213080406189</v>
+        <v>1.25133228302002</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5059173107368674</v>
+        <v>0.9914238516975447</v>
       </c>
       <c r="F2" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9920354917748463</v>
       </c>
       <c r="G2" t="n">
-        <v>64.1040218121336</v>
+        <v>1.758687177428648</v>
       </c>
       <c r="H2" t="n">
-        <v>30.19281732961743</v>
+        <v>1.129233766233765</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>119.1835825443268</v>
+        <v>2.473863124847412</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5359470634249959</v>
+        <v>0.9918212871921988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9923259444363434</v>
       </c>
       <c r="G3" t="n">
-        <v>64.1040218121336</v>
+        <v>1.726321122047857</v>
       </c>
       <c r="H3" t="n">
-        <v>30.19281732961743</v>
+        <v>1.109712337662338</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.299732208251953</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918118579963269</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.109712337662338</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>60.9213080406189</v>
+        <v>1.25133228302002</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5059173107368674</v>
+        <v>0.9914238516975447</v>
       </c>
       <c r="F2" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9920354917748463</v>
       </c>
       <c r="G2" t="n">
-        <v>64.1040218121336</v>
+        <v>1.758687177428648</v>
       </c>
       <c r="H2" t="n">
-        <v>30.19281732961743</v>
+        <v>1.129233766233765</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>119.1835825443268</v>
+        <v>2.473863124847412</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5359470634249959</v>
+        <v>0.9918212871921988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9923259444363434</v>
       </c>
       <c r="G3" t="n">
-        <v>64.1040218121336</v>
+        <v>1.726321122047857</v>
       </c>
       <c r="H3" t="n">
-        <v>30.19281732961743</v>
+        <v>1.109712337662338</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.299732208251953</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918118579963269</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.109712337662338</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.25133228302002</v>
+        <v>14.99010396003723</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9914238516975447</v>
+        <v>0.944227051557548</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9920354917748463</v>
+        <v>0.9498091161774663</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758687177428648</v>
+        <v>39.86621353453122</v>
       </c>
       <c r="H2" t="n">
-        <v>1.129233766233765</v>
+        <v>23.61910385500575</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.473863124847412</v>
+        <v>27.69755601882935</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918212871921988</v>
+        <v>0.9471150885859518</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9923259444363434</v>
+        <v>0.9502406638435245</v>
       </c>
       <c r="G3" t="n">
-        <v>1.726321122047857</v>
+        <v>39.69445612706919</v>
       </c>
       <c r="H3" t="n">
-        <v>1.109712337662338</v>
+        <v>23.63055235903337</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.299732208251953</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918118579963269</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9923259444363434</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.726321122047857</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.109712337662338</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.25133228302002</v>
+        <v>14.99010396003723</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9914238516975447</v>
+        <v>0.944227051557548</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9920354917748463</v>
+        <v>0.9498091161774663</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758687177428648</v>
+        <v>39.86621353453122</v>
       </c>
       <c r="H2" t="n">
-        <v>1.129233766233765</v>
+        <v>23.61910385500575</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.473863124847412</v>
+        <v>27.69755601882935</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918212871921988</v>
+        <v>0.9471150885859518</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9923259444363434</v>
+        <v>0.9502406638435245</v>
       </c>
       <c r="G3" t="n">
-        <v>1.726321122047857</v>
+        <v>39.69445612706919</v>
       </c>
       <c r="H3" t="n">
-        <v>1.109712337662338</v>
+        <v>23.63055235903337</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.299732208251953</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918118579963269</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9923259444363434</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.726321122047857</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.109712337662338</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.99010396003723</v>
+        <v>62.09245896339417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.944227051557548</v>
+        <v>0.999963921679574</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9498091161774663</v>
+        <v>0.9999797479530173</v>
       </c>
       <c r="G2" t="n">
-        <v>39.86621353453122</v>
+        <v>0.04320201350295112</v>
       </c>
       <c r="H2" t="n">
-        <v>23.61910385500575</v>
+        <v>0.01169699744843755</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>27.69755601882935</v>
+        <v>115.0258991718292</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9471150885859518</v>
+        <v>0.9999709085349604</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9502406638435245</v>
+        <v>0.9999797479530173</v>
       </c>
       <c r="G3" t="n">
-        <v>39.69445612706919</v>
+        <v>0.04320201350295112</v>
       </c>
       <c r="H3" t="n">
-        <v>23.63055235903337</v>
+        <v>0.01169699744843755</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>14.99010396003723</v>
+        <v>62.09245896339417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.944227051557548</v>
+        <v>0.999963921679574</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9498091161774663</v>
+        <v>0.9999797479530173</v>
       </c>
       <c r="G2" t="n">
-        <v>39.86621353453122</v>
+        <v>0.04320201350295112</v>
       </c>
       <c r="H2" t="n">
-        <v>23.61910385500575</v>
+        <v>0.01169699744843755</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>27.69755601882935</v>
+        <v>115.0258991718292</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9471150885859518</v>
+        <v>0.9999709085349604</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9502406638435245</v>
+        <v>0.9999797479530173</v>
       </c>
       <c r="G3" t="n">
-        <v>39.69445612706919</v>
+        <v>0.04320201350295112</v>
       </c>
       <c r="H3" t="n">
-        <v>23.63055235903337</v>
+        <v>0.01169699744843755</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>62.09245896339417</v>
+        <v>60.35610222816467</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999963921679574</v>
+        <v>0.5059173107368674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999797479530173</v>
+        <v>0.589358628410138</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04320201350295112</v>
+        <v>64.1040218121336</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01169699744843755</v>
+        <v>30.19281732961743</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>115.0258991718292</v>
+        <v>118.0046970844269</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999709085349604</v>
+        <v>0.5359470634249959</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999797479530173</v>
+        <v>0.589358628410138</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04320201350295112</v>
+        <v>64.1040218121336</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01169699744843755</v>
+        <v>30.19281732961743</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>62.09245896339417</v>
+        <v>60.35610222816467</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999963921679574</v>
+        <v>0.5059173107368674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999797479530173</v>
+        <v>0.589358628410138</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04320201350295112</v>
+        <v>64.1040218121336</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01169699744843755</v>
+        <v>30.19281732961743</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>115.0258991718292</v>
+        <v>118.0046970844269</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999709085349604</v>
+        <v>0.5359470634249959</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999797479530173</v>
+        <v>0.589358628410138</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04320201350295112</v>
+        <v>64.1040218121336</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01169699744843755</v>
+        <v>30.19281732961743</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>60.35610222816467</v>
+        <v>149.8692018985748</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5059173107368674</v>
+        <v>0.9161002400651177</v>
       </c>
       <c r="F2" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9306523814924526</v>
       </c>
       <c r="G2" t="n">
-        <v>64.1040218121336</v>
+        <v>8.93446630697939</v>
       </c>
       <c r="H2" t="n">
-        <v>30.19281732961743</v>
+        <v>5.068721809255267</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>118.0046970844269</v>
+        <v>291.6767017841339</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5359470634249959</v>
+        <v>0.9209918367104901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9306523814924526</v>
       </c>
       <c r="G3" t="n">
-        <v>64.1040218121336</v>
+        <v>8.93446630697939</v>
       </c>
       <c r="H3" t="n">
-        <v>30.19281732961743</v>
+        <v>5.068721809255267</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>60.35610222816467</v>
+        <v>149.8692018985748</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5059173107368674</v>
+        <v>0.9161002400651177</v>
       </c>
       <c r="F2" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9306523814924526</v>
       </c>
       <c r="G2" t="n">
-        <v>64.1040218121336</v>
+        <v>8.93446630697939</v>
       </c>
       <c r="H2" t="n">
-        <v>30.19281732961743</v>
+        <v>5.068721809255267</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>118.0046970844269</v>
+        <v>291.6767017841339</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5359470634249959</v>
+        <v>0.9209918367104901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9306523814924526</v>
       </c>
       <c r="G3" t="n">
-        <v>64.1040218121336</v>
+        <v>8.93446630697939</v>
       </c>
       <c r="H3" t="n">
-        <v>30.19281732961743</v>
+        <v>5.068721809255267</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>149.8692018985748</v>
+        <v>7.273386716842651</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9161002400651177</v>
+        <v>0.4742876429367182</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9306523814924526</v>
+        <v>0.5669789924496238</v>
       </c>
       <c r="G2" t="n">
-        <v>8.93446630697939</v>
+        <v>0.5791054634132733</v>
       </c>
       <c r="H2" t="n">
-        <v>5.068721809255267</v>
+        <v>0.4152397959183673</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>291.6767017841339</v>
+        <v>13.36617517471313</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9209918367104901</v>
+        <v>0.5047939318645751</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9306523814924526</v>
+        <v>0.5669789924496238</v>
       </c>
       <c r="G3" t="n">
-        <v>8.93446630697939</v>
+        <v>0.5791054634132733</v>
       </c>
       <c r="H3" t="n">
-        <v>5.068721809255267</v>
+        <v>0.4152397959183673</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>149.8692018985748</v>
+        <v>7.273386716842651</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9161002400651177</v>
+        <v>0.4742876429367182</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9306523814924526</v>
+        <v>0.5669789924496238</v>
       </c>
       <c r="G2" t="n">
-        <v>8.93446630697939</v>
+        <v>0.5791054634132733</v>
       </c>
       <c r="H2" t="n">
-        <v>5.068721809255267</v>
+        <v>0.4152397959183673</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>291.6767017841339</v>
+        <v>13.36617517471313</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9209918367104901</v>
+        <v>0.5047939318645751</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9306523814924526</v>
+        <v>0.5669789924496238</v>
       </c>
       <c r="G3" t="n">
-        <v>8.93446630697939</v>
+        <v>0.5791054634132733</v>
       </c>
       <c r="H3" t="n">
-        <v>5.068721809255267</v>
+        <v>0.4152397959183673</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.273386716842651</v>
+        <v>1.190144777297974</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4742876429367182</v>
+        <v>0.9914238516975447</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5669789924496238</v>
+        <v>0.9920354917748463</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5791054634132733</v>
+        <v>1.758687177428648</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4152397959183673</v>
+        <v>1.129233766233765</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13.36617517471313</v>
+        <v>2.004979372024536</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5047939318645751</v>
+        <v>0.9918212871921988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5669789924496238</v>
+        <v>0.9923259444363434</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5791054634132733</v>
+        <v>1.726321122047857</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4152397959183673</v>
+        <v>1.109712337662338</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.062476396560669</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918118579963269</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.109712337662338</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.273386716842651</v>
+        <v>1.190144777297974</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4742876429367182</v>
+        <v>0.9914238516975447</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5669789924496238</v>
+        <v>0.9920354917748463</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5791054634132733</v>
+        <v>1.758687177428648</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4152397959183673</v>
+        <v>1.129233766233765</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13.36617517471313</v>
+        <v>2.004979372024536</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5047939318645751</v>
+        <v>0.9918212871921988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5669789924496238</v>
+        <v>0.9923259444363434</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5791054634132733</v>
+        <v>1.726321122047857</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4152397959183673</v>
+        <v>1.109712337662338</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.062476396560669</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918118579963269</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.109712337662338</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.190144777297974</v>
+        <v>1.069406747817993</v>
       </c>
       <c r="E2" t="n">
         <v>0.9914238516975447</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.004979372024536</v>
+        <v>1.803651332855225</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918212871921988</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.062476396560669</v>
+        <v>3.455842971801758</v>
       </c>
       <c r="E4" t="n">
         <v>0.9918118579963269</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.190144777297974</v>
+        <v>1.069406747817993</v>
       </c>
       <c r="E2" t="n">
         <v>0.9914238516975447</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.004979372024536</v>
+        <v>1.803651332855225</v>
       </c>
       <c r="E3" t="n">
         <v>0.9918212871921988</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.062476396560669</v>
+        <v>3.455842971801758</v>
       </c>
       <c r="E4" t="n">
         <v>0.9918118579963269</v>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>1.069406747817993</v>
+        <v>32.65823650360107</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9914238516975447</v>
+        <v>0.9315370185332427</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9920354917748463</v>
+        <v>0.9284488897472609</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758687177428648</v>
+        <v>35.67523815721992</v>
       </c>
       <c r="H2" t="n">
-        <v>1.129233766233765</v>
+        <v>21.55962423986486</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>1.803651332855225</v>
+        <v>65.31638360023499</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918212871921988</v>
+        <v>0.9320700644384793</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9923259444363434</v>
+        <v>0.928334448890752</v>
       </c>
       <c r="G3" t="n">
-        <v>1.726321122047857</v>
+        <v>35.70375674765465</v>
       </c>
       <c r="H3" t="n">
-        <v>1.109712337662338</v>
+        <v>21.68945104166667</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.455842971801758</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918118579963269</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9923259444363434</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.726321122047857</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.109712337662338</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>1.069406747817993</v>
+        <v>32.65823650360107</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9914238516975447</v>
+        <v>0.9315370185332427</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9920354917748463</v>
+        <v>0.9284488897472609</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758687177428648</v>
+        <v>35.67523815721992</v>
       </c>
       <c r="H2" t="n">
-        <v>1.129233766233765</v>
+        <v>21.55962423986486</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>1.803651332855225</v>
+        <v>65.31638360023499</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918212871921988</v>
+        <v>0.9320700644384793</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9923259444363434</v>
+        <v>0.928334448890752</v>
       </c>
       <c r="G3" t="n">
-        <v>1.726321122047857</v>
+        <v>35.70375674765465</v>
       </c>
       <c r="H3" t="n">
-        <v>1.109712337662338</v>
+        <v>21.68945104166667</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.455842971801758</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918118579963269</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9923259444363434</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.726321122047857</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.109712337662338</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>32.65823650360107</v>
+        <v>0.6965103149414062</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9315370185332427</v>
+        <v>0.9914238516975447</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9284488897472609</v>
+        <v>0.9920354917748463</v>
       </c>
       <c r="G2" t="n">
-        <v>35.67523815721992</v>
+        <v>1.758687177428648</v>
       </c>
       <c r="H2" t="n">
-        <v>21.55962423986486</v>
+        <v>1.129233766233765</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>65.31638360023499</v>
+        <v>1.195473909378052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9320700644384793</v>
+        <v>0.9918212871921988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.928334448890752</v>
+        <v>0.9923259444363434</v>
       </c>
       <c r="G3" t="n">
-        <v>35.70375674765465</v>
+        <v>1.726321122047857</v>
       </c>
       <c r="H3" t="n">
-        <v>21.68945104166667</v>
+        <v>1.109712337662338</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.187191247940063</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918118579963269</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.109712337662338</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,26 +654,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>32.65823650360107</v>
+        <v>0.6965103149414062</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9315370185332427</v>
+        <v>0.9914238516975447</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9284488897472609</v>
+        <v>0.9920354917748463</v>
       </c>
       <c r="G2" t="n">
-        <v>35.67523815721992</v>
+        <v>1.758687177428648</v>
       </c>
       <c r="H2" t="n">
-        <v>21.55962423986486</v>
+        <v>1.129233766233765</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -654,26 +689,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>65.31638360023499</v>
+        <v>1.195473909378052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9320700644384793</v>
+        <v>0.9918212871921988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.928334448890752</v>
+        <v>0.9923259444363434</v>
       </c>
       <c r="G3" t="n">
-        <v>35.70375674765465</v>
+        <v>1.726321122047857</v>
       </c>
       <c r="H3" t="n">
-        <v>21.68945104166667</v>
+        <v>1.109712337662338</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.187191247940063</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918118579963269</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.109712337662338</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6965103149414062</v>
+        <v>37.41604208946228</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9914238516975447</v>
+        <v>0.9999687479736658</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9920354917748463</v>
+        <v>0.9999810355680122</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758687177428648</v>
+        <v>0.0412966070481332</v>
       </c>
       <c r="H2" t="n">
-        <v>1.129233766233765</v>
+        <v>0.0109924492759083</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.195473909378052</v>
+        <v>69.43036246299744</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918212871921988</v>
+        <v>0.9999736474855199</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9923259444363434</v>
+        <v>0.9999810355680122</v>
       </c>
       <c r="G3" t="n">
-        <v>1.726321122047857</v>
+        <v>0.0412966070481332</v>
       </c>
       <c r="H3" t="n">
-        <v>1.109712337662338</v>
+        <v>0.0109924492759083</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.187191247940063</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918118579963269</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9923259444363434</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.726321122047857</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.109712337662338</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6965103149414062</v>
+        <v>37.41604208946228</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9914238516975447</v>
+        <v>0.9999687479736658</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9920354917748463</v>
+        <v>0.9999810355680122</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758687177428648</v>
+        <v>0.0412966070481332</v>
       </c>
       <c r="H2" t="n">
-        <v>1.129233766233765</v>
+        <v>0.0109924492759083</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.195473909378052</v>
+        <v>69.43036246299744</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918212871921988</v>
+        <v>0.9999736474855199</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9923259444363434</v>
+        <v>0.9999810355680122</v>
       </c>
       <c r="G3" t="n">
-        <v>1.726321122047857</v>
+        <v>0.0412966070481332</v>
       </c>
       <c r="H3" t="n">
-        <v>1.109712337662338</v>
+        <v>0.0109924492759083</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.187191247940063</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918118579963269</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9923259444363434</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.726321122047857</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.109712337662338</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Bagging_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>37.41604208946228</v>
+        <v>37.30611491203308</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999687479736658</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>69.43036246299744</v>
+        <v>69.11179947853088</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999736474855199</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>37.41604208946228</v>
+        <v>37.30611491203308</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999687479736658</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>69.43036246299744</v>
+        <v>69.11179947853088</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999736474855199</v>
